--- a/feedback_surveys/019_multi_stakeholder_feedback_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/019_multi_stakeholder_feedback_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -914,12 +914,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_'11-1',_'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': '11-1', 'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1304,46 +1304,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_'11-2',_'label':_'applicable'}</t>
+          <t>applicable</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': '11-2', 'label': 'Applicable'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>project_sponsor_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'id':_'11-3',_'label':_'not_applicable'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'id': '11-3', 'label': 'Not Applicable'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>project_sponsor_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'id':_'11-4',_'label':_'applicable'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'id': '11-4', 'label': 'Applicable'}</t>
+          <t>Applicable</t>
         </is>
       </c>
     </row>
